--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Tez\tablolar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmeliht/Desktop/URL-Phishing-Detection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A1CAD5-74AD-42C5-B64A-8759CFD78FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA630591-FD20-4E40-AD68-7796ED887B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sayfa2" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa1!$A$1:$A$118</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="336">
   <si>
     <t>No</t>
   </si>
@@ -1074,12 +1074,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1118,7 +1124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1135,10 +1141,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1148,11 +1150,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1453,28 +1471,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O337"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
       <c r="J1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1523,7 +1541,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1549,7 +1567,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1578,7 +1596,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1607,7 +1625,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1636,7 +1654,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1665,7 +1683,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1694,7 +1712,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1723,7 +1741,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1752,7 +1770,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1781,7 +1799,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1810,7 +1828,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1839,7 +1857,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1868,7 +1886,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1897,7 +1915,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1926,7 +1944,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1955,7 +1973,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1984,7 +2002,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2007,7 +2025,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2030,7 +2048,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2053,7 +2071,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2076,7 +2094,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2099,7 +2117,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2122,7 +2140,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2145,7 +2163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2168,7 +2186,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2191,7 +2209,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2214,7 +2232,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2237,7 +2255,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2260,7 +2278,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2283,7 +2301,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2306,7 +2324,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2329,7 +2347,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2352,7 +2370,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2375,7 +2393,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2398,7 +2416,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2421,7 +2439,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2444,7 +2462,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2467,7 +2485,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2490,7 +2508,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2513,15 +2531,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>289</v>
       </c>
       <c r="J50" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>195</v>
       </c>
@@ -2541,7 +2559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>1</v>
       </c>
@@ -2561,7 +2579,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2</v>
       </c>
@@ -2581,7 +2599,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>3</v>
       </c>
@@ -2601,7 +2619,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>4</v>
       </c>
@@ -2621,7 +2639,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>5</v>
       </c>
@@ -2641,7 +2659,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>6</v>
       </c>
@@ -2661,7 +2679,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>7</v>
       </c>
@@ -2681,7 +2699,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>8</v>
       </c>
@@ -2701,7 +2719,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>9</v>
       </c>
@@ -2721,7 +2739,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>10</v>
       </c>
@@ -2741,7 +2759,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>11</v>
       </c>
@@ -2761,7 +2779,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>12</v>
       </c>
@@ -2781,7 +2799,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>13</v>
       </c>
@@ -2801,7 +2819,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>14</v>
       </c>
@@ -2821,7 +2839,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>15</v>
       </c>
@@ -2841,7 +2859,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>16</v>
       </c>
@@ -2861,7 +2879,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>17</v>
       </c>
@@ -2881,7 +2899,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>18</v>
       </c>
@@ -2901,7 +2919,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>19</v>
       </c>
@@ -2921,7 +2939,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>20</v>
       </c>
@@ -2941,7 +2959,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>21</v>
       </c>
@@ -2961,7 +2979,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>22</v>
       </c>
@@ -2981,7 +2999,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>23</v>
       </c>
@@ -3001,7 +3019,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>24</v>
       </c>
@@ -3012,7 +3030,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>25</v>
       </c>
@@ -3023,7 +3041,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>26</v>
       </c>
@@ -3034,7 +3052,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>27</v>
       </c>
@@ -3045,7 +3063,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>28</v>
       </c>
@@ -3056,7 +3074,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>29</v>
       </c>
@@ -3067,7 +3085,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>30</v>
       </c>
@@ -3078,7 +3096,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>31</v>
       </c>
@@ -3089,7 +3107,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>32</v>
       </c>
@@ -3100,7 +3118,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>33</v>
       </c>
@@ -3111,7 +3129,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>34</v>
       </c>
@@ -3122,7 +3140,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>35</v>
       </c>
@@ -3133,7 +3151,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>36</v>
       </c>
@@ -3144,7 +3162,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>37</v>
       </c>
@@ -3155,7 +3173,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>38</v>
       </c>
@@ -3166,7 +3184,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>39</v>
       </c>
@@ -3177,7 +3195,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>40</v>
       </c>
@@ -3188,7 +3206,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>41</v>
       </c>
@@ -3199,7 +3217,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>42</v>
       </c>
@@ -3210,7 +3228,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>43</v>
       </c>
@@ -3221,7 +3239,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>44</v>
       </c>
@@ -3232,7 +3250,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>45</v>
       </c>
@@ -3243,7 +3261,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>46</v>
       </c>
@@ -3254,7 +3272,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>47</v>
       </c>
@@ -3265,588 +3283,588 @@
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
     </row>
-    <row r="105" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="8"/>
-    </row>
-    <row r="107" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B107" s="9"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="10"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="10"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="10"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="10"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="10"/>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B113" s="10"/>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B114" s="10"/>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B115" s="10"/>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B116" s="10"/>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B117" s="10"/>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" s="10"/>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B119" s="10"/>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B120" s="10"/>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B121" s="10"/>
-    </row>
-    <row r="125" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B125" s="9"/>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B126" s="10"/>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B127" s="10"/>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B128" s="10"/>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B129" s="10"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B130" s="10"/>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B131" s="10"/>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B132" s="10"/>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B133" s="10"/>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B134" s="10"/>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B135" s="10"/>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B136" s="10"/>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B137" s="10"/>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B138" s="10"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="10"/>
-    </row>
-    <row r="143" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B143" s="9"/>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B144" s="10"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145" s="10"/>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146" s="10"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="10"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148" s="10"/>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149" s="10"/>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B150" s="10"/>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B151" s="10"/>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" s="10"/>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B153" s="10"/>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B154" s="10"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B155" s="10"/>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B156" s="10"/>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157" s="10"/>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B158" s="10"/>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B159" s="10"/>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B160" s="10"/>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B161" s="10"/>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B162" s="10"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B163" s="10"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B164" s="10"/>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B165" s="10"/>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B166" s="10"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B167" s="10"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B168" s="10"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B169" s="10"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B170" s="10"/>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B171" s="10"/>
-    </row>
-    <row r="175" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B175" s="9"/>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B176" s="10"/>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B177" s="10"/>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B178" s="10"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B179" s="10"/>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B180" s="10"/>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B181" s="10"/>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B182" s="10"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B183" s="10"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B184" s="10"/>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B185" s="10"/>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B186" s="10"/>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B187" s="10"/>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B188" s="10"/>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B189" s="10"/>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B190" s="10"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B191" s="10"/>
-    </row>
-    <row r="195" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B195" s="9"/>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B196" s="10"/>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B197" s="10"/>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B198" s="10"/>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B199" s="10"/>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B200" s="10"/>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B201" s="10"/>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B202" s="10"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B203" s="10"/>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B204" s="10"/>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B205" s="10"/>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B206" s="10"/>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B207" s="10"/>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B208" s="10"/>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B209" s="10"/>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B210" s="10"/>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B211" s="10"/>
-    </row>
-    <row r="215" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B215" s="9"/>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B216" s="10"/>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B217" s="10"/>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B218" s="10"/>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B219" s="10"/>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B220" s="10"/>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B221" s="10"/>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B222" s="10"/>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B223" s="10"/>
-    </row>
-    <row r="227" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B227" s="9"/>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B228" s="10"/>
-    </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B229" s="10"/>
-    </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B230" s="10"/>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B231" s="10"/>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B232" s="10"/>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B233" s="10"/>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B234" s="10"/>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B235" s="10"/>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B236" s="10"/>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B237" s="10"/>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B238" s="10"/>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B239" s="10"/>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B240" s="10"/>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B241" s="10"/>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B242" s="10"/>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B243" s="10"/>
-    </row>
-    <row r="247" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B247" s="9"/>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B248" s="10"/>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B249" s="10"/>
-    </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B250" s="10"/>
-    </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B251" s="10"/>
-    </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B252" s="10"/>
-    </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B253" s="10"/>
-    </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B254" s="10"/>
-    </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B255" s="10"/>
-    </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B256" s="10"/>
-    </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B257" s="10"/>
-    </row>
-    <row r="261" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B261" s="9"/>
-    </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B262" s="10"/>
-    </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B263" s="10"/>
-    </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B264" s="10"/>
-    </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B265" s="10"/>
-    </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B266" s="10"/>
-    </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B267" s="10"/>
-    </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B268" s="10"/>
-    </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B269" s="10"/>
-    </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B270" s="10"/>
-    </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B271" s="10"/>
-    </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B272" s="10"/>
-    </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B273" s="10"/>
-    </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B274" s="10"/>
-    </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B275" s="10"/>
-    </row>
-    <row r="279" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B279" s="9"/>
-    </row>
-    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B280" s="10"/>
-    </row>
-    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B281" s="10"/>
-    </row>
-    <row r="282" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B282" s="10"/>
-    </row>
-    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B283" s="10"/>
-    </row>
-    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B284" s="10"/>
-    </row>
-    <row r="285" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B285" s="10"/>
-    </row>
-    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B286" s="10"/>
-    </row>
-    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B287" s="10"/>
-    </row>
-    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B288" s="10"/>
-    </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B289" s="10"/>
-    </row>
-    <row r="293" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B293" s="9"/>
-    </row>
-    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B294" s="10"/>
-    </row>
-    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B295" s="10"/>
-    </row>
-    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B296" s="10"/>
-    </row>
-    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B297" s="10"/>
-    </row>
-    <row r="301" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B301" s="9"/>
-    </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B302" s="10"/>
-    </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B303" s="10"/>
-    </row>
-    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B304" s="10"/>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" s="10"/>
-    </row>
-    <row r="309" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B309" s="9"/>
-    </row>
-    <row r="310" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B310" s="10"/>
-    </row>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B311" s="10"/>
-    </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B312" s="10"/>
-    </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B313" s="10"/>
-    </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B314" s="10"/>
-    </row>
-    <row r="315" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B315" s="10"/>
-    </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B316" s="10"/>
-    </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B317" s="10"/>
-    </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B318" s="10"/>
-    </row>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B319" s="10"/>
-    </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B320" s="10"/>
-    </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B321" s="10"/>
-    </row>
-    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B322" s="10"/>
-    </row>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B323" s="10"/>
-    </row>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B324" s="10"/>
-    </row>
-    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B325" s="10"/>
-    </row>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B326" s="10"/>
-    </row>
-    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B327" s="10"/>
-    </row>
-    <row r="328" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B328" s="10"/>
-    </row>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B329" s="10"/>
-    </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B330" s="10"/>
-    </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B331" s="10"/>
-    </row>
-    <row r="335" spans="2:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="B335" s="9"/>
-    </row>
-    <row r="336" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B336" s="10"/>
-    </row>
-    <row r="337" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B337" s="10"/>
+    <row r="105" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="B105" s="6"/>
+    </row>
+    <row r="107" spans="1:3" ht="19" x14ac:dyDescent="0.2">
+      <c r="B107" s="7"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B108" s="8"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B109" s="8"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B110" s="8"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B111" s="8"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B112" s="8"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="8"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="8"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="8"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="8"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="8"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="8"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="8"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="8"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="8"/>
+    </row>
+    <row r="125" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B125" s="7"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="8"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="8"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="8"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="8"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="8"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="8"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="8"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="8"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="8"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="8"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="8"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="8"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="8"/>
+    </row>
+    <row r="143" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B143" s="7"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="8"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="8"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="8"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="8"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="8"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="8"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="8"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" s="8"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="8"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="8"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="8"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" s="8"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="8"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="8"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="8"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="8"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="8"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="8"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="8"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="8"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="8"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="8"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="8"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="8"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="8"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="8"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="8"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="8"/>
+    </row>
+    <row r="175" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B175" s="7"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="8"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="8"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="8"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="8"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="8"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="8"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="8"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="8"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="8"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" s="8"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" s="8"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187" s="8"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188" s="8"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" s="8"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" s="8"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" s="8"/>
+    </row>
+    <row r="195" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B195" s="7"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B196" s="8"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B197" s="8"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B198" s="8"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199" s="8"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B200" s="8"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B201" s="8"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B202" s="8"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B203" s="8"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B204" s="8"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205" s="8"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B206" s="8"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B207" s="8"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208" s="8"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B209" s="8"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210" s="8"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B211" s="8"/>
+    </row>
+    <row r="215" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B215" s="7"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216" s="8"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B217" s="8"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218" s="8"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B219" s="8"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220" s="8"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" s="8"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222" s="8"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" s="8"/>
+    </row>
+    <row r="227" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B227" s="7"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228" s="8"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229" s="8"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230" s="8"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231" s="8"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" s="8"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233" s="8"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" s="8"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235" s="8"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236" s="8"/>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B237" s="8"/>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B238" s="8"/>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B239" s="8"/>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B240" s="8"/>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241" s="8"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B242" s="8"/>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243" s="8"/>
+    </row>
+    <row r="247" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B247" s="7"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248" s="8"/>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B249" s="8"/>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B250" s="8"/>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B251" s="8"/>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B252" s="8"/>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B253" s="8"/>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B254" s="8"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B255" s="8"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B256" s="8"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B257" s="8"/>
+    </row>
+    <row r="261" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B261" s="7"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B262" s="8"/>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B263" s="8"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B264" s="8"/>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B265" s="8"/>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B266" s="8"/>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B267" s="8"/>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B268" s="8"/>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B269" s="8"/>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B270" s="8"/>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B271" s="8"/>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B272" s="8"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B273" s="8"/>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B274" s="8"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B275" s="8"/>
+    </row>
+    <row r="279" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B279" s="7"/>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B280" s="8"/>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B281" s="8"/>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B282" s="8"/>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B283" s="8"/>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B284" s="8"/>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B285" s="8"/>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B286" s="8"/>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B287" s="8"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B288" s="8"/>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B289" s="8"/>
+    </row>
+    <row r="293" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B293" s="7"/>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B294" s="8"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B295" s="8"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B296" s="8"/>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B297" s="8"/>
+    </row>
+    <row r="301" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B301" s="7"/>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B302" s="8"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B303" s="8"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B304" s="8"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B305" s="8"/>
+    </row>
+    <row r="309" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B309" s="7"/>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B310" s="8"/>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B311" s="8"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B312" s="8"/>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B313" s="8"/>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B314" s="8"/>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B315" s="8"/>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B316" s="8"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B317" s="8"/>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B318" s="8"/>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B319" s="8"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B320" s="8"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B321" s="8"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B322" s="8"/>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B323" s="8"/>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B324" s="8"/>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B325" s="8"/>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B326" s="8"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B327" s="8"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B328" s="8"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B329" s="8"/>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B330" s="8"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B331" s="8"/>
+    </row>
+    <row r="335" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+      <c r="B335" s="7"/>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B336" s="8"/>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B337" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3854,4 +3872,1006 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A007D-C471-794C-B50E-1874592152EF}">
+  <dimension ref="A1:D118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A116" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A117" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A118" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A118">
+    <sortCondition ref="A1:A118"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66078BF-7097-A04E-85DC-24CEE7935F32}">
+  <dimension ref="A1:A76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmeliht/Desktop/URL-Phishing-Detection/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA630591-FD20-4E40-AD68-7796ED887B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE4641D-9AE8-415C-A0C4-8584948D911E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sayfa2" sheetId="3" r:id="rId3"/>
+    <sheet name="feature_result" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa1!$A$1:$A$118</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1150,27 +1155,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1471,28 +1467,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O337"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
       <c r="J1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1515,7 +1511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1541,7 +1537,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1567,7 +1563,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1596,7 +1592,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1625,7 +1621,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1654,7 +1650,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1683,7 +1679,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1712,7 +1708,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1741,7 +1737,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1770,7 +1766,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1799,7 +1795,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1828,7 +1824,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1857,7 +1853,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1886,7 +1882,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1915,7 +1911,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1944,7 +1940,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1973,7 +1969,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2002,7 +1998,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2025,7 +2021,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2048,7 +2044,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2071,7 +2067,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2094,7 +2090,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2117,7 +2113,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2140,7 +2136,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2163,7 +2159,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2186,7 +2182,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2209,7 +2205,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2232,7 +2228,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2255,7 +2251,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2278,7 +2274,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2301,7 +2297,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2324,7 +2320,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2347,7 +2343,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2370,7 +2366,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2393,7 +2389,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2416,7 +2412,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2439,7 +2435,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2462,7 +2458,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2485,7 +2481,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2508,7 +2504,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2531,7 +2527,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>289</v>
       </c>
@@ -2539,7 +2535,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>195</v>
       </c>
@@ -2559,7 +2555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>1</v>
       </c>
@@ -2579,7 +2575,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>2</v>
       </c>
@@ -2599,7 +2595,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>3</v>
       </c>
@@ -2619,7 +2615,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>4</v>
       </c>
@@ -2639,7 +2635,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>5</v>
       </c>
@@ -2659,7 +2655,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>6</v>
       </c>
@@ -2679,7 +2675,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>7</v>
       </c>
@@ -2699,7 +2695,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>8</v>
       </c>
@@ -2719,7 +2715,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>9</v>
       </c>
@@ -2739,7 +2735,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>10</v>
       </c>
@@ -2759,7 +2755,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>11</v>
       </c>
@@ -2779,7 +2775,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>12</v>
       </c>
@@ -2799,7 +2795,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>13</v>
       </c>
@@ -2819,7 +2815,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>14</v>
       </c>
@@ -2839,7 +2835,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>15</v>
       </c>
@@ -2859,7 +2855,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>16</v>
       </c>
@@ -2879,7 +2875,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>17</v>
       </c>
@@ -2899,7 +2895,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>18</v>
       </c>
@@ -2919,7 +2915,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>19</v>
       </c>
@@ -2939,7 +2935,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>20</v>
       </c>
@@ -2959,7 +2955,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>21</v>
       </c>
@@ -2979,7 +2975,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>22</v>
       </c>
@@ -2999,7 +2995,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>23</v>
       </c>
@@ -3019,7 +3015,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>24</v>
       </c>
@@ -3030,7 +3026,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>25</v>
       </c>
@@ -3041,7 +3037,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>26</v>
       </c>
@@ -3052,7 +3048,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>27</v>
       </c>
@@ -3063,7 +3059,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>28</v>
       </c>
@@ -3074,7 +3070,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>29</v>
       </c>
@@ -3085,7 +3081,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>30</v>
       </c>
@@ -3096,7 +3092,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>31</v>
       </c>
@@ -3107,7 +3103,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>32</v>
       </c>
@@ -3118,7 +3114,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>33</v>
       </c>
@@ -3129,7 +3125,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>34</v>
       </c>
@@ -3140,7 +3136,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>35</v>
       </c>
@@ -3151,7 +3147,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>36</v>
       </c>
@@ -3162,7 +3158,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>37</v>
       </c>
@@ -3173,7 +3169,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>38</v>
       </c>
@@ -3184,7 +3180,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>39</v>
       </c>
@@ -3195,7 +3191,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>40</v>
       </c>
@@ -3206,7 +3202,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>41</v>
       </c>
@@ -3217,7 +3213,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>42</v>
       </c>
@@ -3228,7 +3224,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>43</v>
       </c>
@@ -3239,7 +3235,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>44</v>
       </c>
@@ -3250,7 +3246,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>45</v>
       </c>
@@ -3261,7 +3257,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>46</v>
       </c>
@@ -3272,7 +3268,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>47</v>
       </c>
@@ -3283,587 +3279,587 @@
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
     </row>
-    <row r="105" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B105" s="6"/>
     </row>
-    <row r="107" spans="1:3" ht="19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B107" s="7"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B108" s="8"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B109" s="8"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B110" s="8"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B111" s="8"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B112" s="8"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="8"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" s="8"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" s="8"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" s="8"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" s="8"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="8"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" s="8"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" s="8"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" s="8"/>
     </row>
-    <row r="125" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B125" s="7"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B126" s="8"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B127" s="8"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B128" s="8"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B129" s="8"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B130" s="8"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B131" s="8"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B132" s="8"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B133" s="8"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B134" s="8"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B135" s="8"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B136" s="8"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B137" s="8"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B138" s="8"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B139" s="8"/>
     </row>
-    <row r="143" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B143" s="7"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B144" s="8"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B145" s="8"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B146" s="8"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="8"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="8"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B149" s="8"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B150" s="8"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B151" s="8"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B152" s="8"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B153" s="8"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B154" s="8"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B155" s="8"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B156" s="8"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B157" s="8"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B158" s="8"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="8"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B160" s="8"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B161" s="8"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B162" s="8"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B163" s="8"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B164" s="8"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B165" s="8"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B166" s="8"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B167" s="8"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B168" s="8"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B169" s="8"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B170" s="8"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="8"/>
     </row>
-    <row r="175" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B176" s="8"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B177" s="8"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B178" s="8"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="8"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B180" s="8"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B181" s="8"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B182" s="8"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B183" s="8"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B184" s="8"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B185" s="8"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B186" s="8"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B187" s="8"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B188" s="8"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B189" s="8"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B190" s="8"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B191" s="8"/>
     </row>
-    <row r="195" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B195" s="7"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="8"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B197" s="8"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B198" s="8"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B199" s="8"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B200" s="8"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B201" s="8"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B202" s="8"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B203" s="8"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B204" s="8"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B205" s="8"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B206" s="8"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B207" s="8"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B208" s="8"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B209" s="8"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B210" s="8"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B211" s="8"/>
     </row>
-    <row r="215" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B215" s="7"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B216" s="8"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B217" s="8"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B218" s="8"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="8"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="8"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B221" s="8"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B222" s="8"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B223" s="8"/>
     </row>
-    <row r="227" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B227" s="7"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B228" s="8"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B229" s="8"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B230" s="8"/>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B231" s="8"/>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B232" s="8"/>
     </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B233" s="8"/>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B234" s="8"/>
     </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B235" s="8"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B236" s="8"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B237" s="8"/>
     </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B238" s="8"/>
     </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B239" s="8"/>
     </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B240" s="8"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B241" s="8"/>
     </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B242" s="8"/>
     </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="8"/>
     </row>
-    <row r="247" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B247" s="7"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B248" s="8"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B249" s="8"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B250" s="8"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B251" s="8"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B252" s="8"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B253" s="8"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B254" s="8"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B255" s="8"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B256" s="8"/>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B257" s="8"/>
     </row>
-    <row r="261" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B261" s="7"/>
     </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B262" s="8"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B263" s="8"/>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B264" s="8"/>
     </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B265" s="8"/>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B266" s="8"/>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B267" s="8"/>
     </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B268" s="8"/>
     </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B269" s="8"/>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B270" s="8"/>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B271" s="8"/>
     </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B272" s="8"/>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B273" s="8"/>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B274" s="8"/>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B275" s="8"/>
     </row>
-    <row r="279" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B279" s="7"/>
     </row>
-    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B280" s="8"/>
     </row>
-    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B281" s="8"/>
     </row>
-    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="282" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B282" s="8"/>
     </row>
-    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B283" s="8"/>
     </row>
-    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B284" s="8"/>
     </row>
-    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="285" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B285" s="8"/>
     </row>
-    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B286" s="8"/>
     </row>
-    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B287" s="8"/>
     </row>
-    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B288" s="8"/>
     </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B289" s="8"/>
     </row>
-    <row r="293" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="293" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B293" s="7"/>
     </row>
-    <row r="294" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B294" s="8"/>
     </row>
-    <row r="295" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B295" s="8"/>
     </row>
-    <row r="296" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B296" s="8"/>
     </row>
-    <row r="297" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B297" s="8"/>
     </row>
-    <row r="301" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="301" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B301" s="7"/>
     </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="302" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B302" s="8"/>
     </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B303" s="8"/>
     </row>
-    <row r="304" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B304" s="8"/>
     </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B305" s="8"/>
     </row>
-    <row r="309" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="309" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B309" s="7"/>
     </row>
-    <row r="310" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="310" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B310" s="8"/>
     </row>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B311" s="8"/>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B312" s="8"/>
     </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B313" s="8"/>
     </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B314" s="8"/>
     </row>
-    <row r="315" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="315" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B315" s="8"/>
     </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B316" s="8"/>
     </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B317" s="8"/>
     </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B318" s="8"/>
     </row>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B319" s="8"/>
     </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B320" s="8"/>
     </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B321" s="8"/>
     </row>
-    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B322" s="8"/>
     </row>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B323" s="8"/>
     </row>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B324" s="8"/>
     </row>
-    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B325" s="8"/>
     </row>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="326" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B326" s="8"/>
     </row>
-    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B327" s="8"/>
     </row>
-    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B328" s="8"/>
     </row>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B329" s="8"/>
     </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B330" s="8"/>
     </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B331" s="8"/>
     </row>
-    <row r="335" spans="2:2" ht="19" x14ac:dyDescent="0.2">
+    <row r="335" spans="2:2" ht="18" x14ac:dyDescent="0.25">
       <c r="B335" s="7"/>
     </row>
-    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B336" s="8"/>
     </row>
-    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B337" s="8"/>
     </row>
   </sheetData>
@@ -3877,600 +3873,600 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A007D-C471-794C-B50E-1874592152EF}">
   <dimension ref="A1:D118"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>329</v>
       </c>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="10" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="9" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="10" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="10" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="10" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="10" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="10" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="10" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="10" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="10" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="10" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="11" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A117" s="10" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>196</v>
       </c>
@@ -4486,387 +4482,387 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66078BF-7097-A04E-85DC-24CEE7935F32}">
   <dimension ref="A1:A76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>196</v>
       </c>

--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE4641D-9AE8-415C-A0C4-8584948D911E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86226964-3A49-4A42-A53B-EC61343C3986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="400">
   <si>
     <t>No</t>
   </si>
@@ -1040,13 +1040,205 @@
   </si>
   <si>
     <t>Malicious_URL_Detection_and_Categorization_Using_Machine_Learning_Techniques</t>
+  </si>
+  <si>
+    <t>LengthOfURL</t>
+  </si>
+  <si>
+    <t>DomainLengthOfURL</t>
+  </si>
+  <si>
+    <t>Having_Path</t>
+  </si>
+  <si>
+    <t>ShannonEntropy</t>
+  </si>
+  <si>
+    <t>KolmogorovComplexity</t>
+  </si>
+  <si>
+    <t>HexPatternCnt</t>
+  </si>
+  <si>
+    <t>Base64PatternCnt</t>
+  </si>
+  <si>
+    <t>Average_Word</t>
+  </si>
+  <si>
+    <t>Base64_Pattern_Cnt</t>
+  </si>
+  <si>
+    <t>Check_EXE</t>
+  </si>
+  <si>
+    <t>Check_IP_HostName</t>
+  </si>
+  <si>
+    <t>Count_%</t>
+  </si>
+  <si>
+    <t>Count_/</t>
+  </si>
+  <si>
+    <t>Count_All_Functions</t>
+  </si>
+  <si>
+    <t>Count_Digit</t>
+  </si>
+  <si>
+    <t>Count_Dir</t>
+  </si>
+  <si>
+    <t>Count_Dot</t>
+  </si>
+  <si>
+    <t>Count_Embed_Domain</t>
+  </si>
+  <si>
+    <t>Orijinal</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Character _Repetition</t>
+  </si>
+  <si>
+    <t>Count_Letter</t>
+  </si>
+  <si>
+    <t>Count_Path_Slash</t>
+  </si>
+  <si>
+    <t>Count_Search</t>
+  </si>
+  <si>
+    <t>Count_Symbols</t>
+  </si>
+  <si>
+    <t>Count-Http</t>
+  </si>
+  <si>
+    <t>Count-Https</t>
+  </si>
+  <si>
+    <t>Count_www</t>
+  </si>
+  <si>
+    <t>Dash_Char_Count</t>
+  </si>
+  <si>
+    <t>Delimiter_Count</t>
+  </si>
+  <si>
+    <t>Digit_Alphabet_Ratio</t>
+  </si>
+  <si>
+    <t>Digits_in_Domain_Name</t>
+  </si>
+  <si>
+    <t>Digits_in_Host</t>
+  </si>
+  <si>
+    <t>Dist_Digit_Alphabet</t>
+  </si>
+  <si>
+    <t>Dist_Word_Based</t>
+  </si>
+  <si>
+    <t>Domain_Name</t>
+  </si>
+  <si>
+    <t>Domain_Length_Of_URL</t>
+  </si>
+  <si>
+    <t>Domain_URL_Ratio</t>
+  </si>
+  <si>
+    <t>Double_Slash_Count</t>
+  </si>
+  <si>
+    <t>File_Extension</t>
+  </si>
+  <si>
+    <t>FTP_Used</t>
+  </si>
+  <si>
+    <t>Hash_Char_Count</t>
+  </si>
+  <si>
+    <t>Hex_Pattern_Cnt</t>
+  </si>
+  <si>
+    <t>Host_Length</t>
+  </si>
+  <si>
+    <t>Host_Precense_Of_Digit</t>
+  </si>
+  <si>
+    <t>IP_Address</t>
+  </si>
+  <si>
+    <t>Kolmogorov_Complexity</t>
+  </si>
+  <si>
+    <t>Length_OfURL</t>
+  </si>
+  <si>
+    <t>Longest_Word</t>
+  </si>
+  <si>
+    <t>Longest_Word_in_Hostname</t>
+  </si>
+  <si>
+    <t>Longest/Shortest _Word_Length</t>
+  </si>
+  <si>
+    <t>Numeric_Char_Count</t>
+  </si>
+  <si>
+    <t>Path_Length</t>
+  </si>
+  <si>
+    <t>Percent_Char_Count</t>
+  </si>
+  <si>
+    <t>Port_Number</t>
+  </si>
+  <si>
+    <t>Query_Length</t>
+  </si>
+  <si>
+    <t>Semi_Col_Count</t>
+  </si>
+  <si>
+    <t>Shortest_Word</t>
+  </si>
+  <si>
+    <t>Special_Char_Alphabet_Ratio</t>
+  </si>
+  <si>
+    <t>STD_of_Words_Length</t>
+  </si>
+  <si>
+    <t>Tld_Length</t>
+  </si>
+  <si>
+    <t>Uppercase_Lowercase_Ratio</t>
+  </si>
+  <si>
+    <t>URL_Without_www</t>
+  </si>
+  <si>
+    <t>Short_Url</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1078,8 +1270,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1089,6 +1295,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1129,7 +1341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1162,6 +1374,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4481,393 +4704,658 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66078BF-7097-A04E-85DC-24CEE7935F32}">
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="39" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="E9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>348</v>
+      </c>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="E14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E15" t="s">
+        <v>349</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="E16" t="s">
+        <v>350</v>
+      </c>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="E17" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="E18" t="s">
+        <v>352</v>
+      </c>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="E19" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="E20" t="s">
+        <v>357</v>
+      </c>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="E21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="E22" t="s">
+        <v>359</v>
+      </c>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="E23" t="s">
+        <v>360</v>
+      </c>
+      <c r="G23" s="13"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="E24" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="E25" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E26" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G26" s="13"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E29" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="E31" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E32" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E33" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="E36" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="E38" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="E39" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="E40" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="E41" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="E42" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="E43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>341</v>
+      </c>
+      <c r="E45" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="E46" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="E47" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="E48" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="E49" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>340</v>
+      </c>
+      <c r="E50" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="E51" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="E53" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="E54" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="E55" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="E56" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="E57" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="E58" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="E59" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="E60" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="E61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="E62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>339</v>
+      </c>
+      <c r="E63" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="E64" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="E65" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="E66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="E67" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="E68" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
+      <c r="E69" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="E70" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="E72" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+      <c r="E73" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="E74" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="E75" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
+      <c r="E76" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>196</v>
+      <c r="E77" s="4" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
+    <sortCondition ref="A2:A77"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86226964-3A49-4A42-A53B-EC61343C3986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77917FC-B823-44D7-8CC7-9D82380C8B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="398">
   <si>
     <t>No</t>
   </si>
@@ -1072,9 +1072,6 @@
     <t>Check_EXE</t>
   </si>
   <si>
-    <t>Check_IP_HostName</t>
-  </si>
-  <si>
     <t>Count_%</t>
   </si>
   <si>
@@ -1175,9 +1172,6 @@
   </si>
   <si>
     <t>Host_Precense_Of_Digit</t>
-  </si>
-  <si>
-    <t>IP_Address</t>
   </si>
   <si>
     <t>Kolmogorov_Complexity</t>
@@ -4704,7 +4698,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66078BF-7097-A04E-85DC-24CEE7935F32}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -4714,10 +4708,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>354</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4742,7 +4736,7 @@
         <v>212</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G4" s="13"/>
     </row>
@@ -4756,89 +4750,89 @@
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="A6" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>346</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="G7" s="13"/>
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>347</v>
       </c>
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>150</v>
       </c>
       <c r="G10" s="13"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>154</v>
+        <v>348</v>
       </c>
       <c r="G14" s="13"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>349</v>
@@ -4846,44 +4840,44 @@
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="A16" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>350</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" t="s">
         <v>351</v>
       </c>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>353</v>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>356</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
         <v>357</v>
@@ -4892,7 +4886,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
         <v>358</v>
@@ -4901,7 +4895,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
         <v>359</v>
@@ -4909,156 +4903,155 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="A23" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>360</v>
       </c>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="G24" s="13"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
         <v>363</v>
       </c>
-      <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="A28" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="A30" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="A35" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>221</v>
+        <v>337</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E38" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="A39" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
         <v>375</v>
@@ -5066,47 +5059,47 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="A43" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+      <c r="E44" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>338</v>
-      </c>
-    </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>341</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="A45" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" t="s">
         <v>378</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E47" t="s">
         <v>379</v>
@@ -5114,247 +5107,231 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>340</v>
       </c>
       <c r="E48" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="A49" t="s">
+        <v>122</v>
+      </c>
+      <c r="E49" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>340</v>
-      </c>
-      <c r="E50" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>122</v>
-      </c>
-      <c r="E51" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>336</v>
+        <v>226</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E54" s="4" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E55" s="4" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>137</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="A57" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="A58" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E59" s="4" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>339</v>
       </c>
       <c r="E61" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="E62" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>339</v>
-      </c>
-      <c r="E63" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" t="s">
-        <v>394</v>
+      <c r="A66" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>202</v>
+        <v>323</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>202</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>217</v>
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>323</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>28</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>396</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>39</v>
-      </c>
-      <c r="E75" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A75" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>228</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
-    <sortCondition ref="A2:A77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A75">
+    <sortCondition ref="A2:A75"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77917FC-B823-44D7-8CC7-9D82380C8B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CE3E9C-BDCC-4CAC-9B67-0D90B7976A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa1" sheetId="2" r:id="rId2"/>
     <sheet name="feature_result" sheetId="3" r:id="rId3"/>
+    <sheet name="Sayfa2" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">feature_result!$E$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa1!$A$1:$A$118</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="390">
   <si>
     <t>No</t>
   </si>
@@ -1078,9 +1080,6 @@
     <t>Count_/</t>
   </si>
   <si>
-    <t>Count_All_Functions</t>
-  </si>
-  <si>
     <t>Count_Digit</t>
   </si>
   <si>
@@ -1108,45 +1107,12 @@
     <t>Count_Path_Slash</t>
   </si>
   <si>
-    <t>Count_Search</t>
-  </si>
-  <si>
-    <t>Count_Symbols</t>
-  </si>
-  <si>
-    <t>Count-Http</t>
-  </si>
-  <si>
-    <t>Count-Https</t>
-  </si>
-  <si>
     <t>Count_www</t>
   </si>
   <si>
-    <t>Dash_Char_Count</t>
-  </si>
-  <si>
-    <t>Delimiter_Count</t>
-  </si>
-  <si>
     <t>Digit_Alphabet_Ratio</t>
   </si>
   <si>
-    <t>Digits_in_Domain_Name</t>
-  </si>
-  <si>
-    <t>Digits_in_Host</t>
-  </si>
-  <si>
-    <t>Dist_Digit_Alphabet</t>
-  </si>
-  <si>
-    <t>Dist_Word_Based</t>
-  </si>
-  <si>
-    <t>Domain_Name</t>
-  </si>
-  <si>
     <t>Domain_Length_Of_URL</t>
   </si>
   <si>
@@ -1177,9 +1143,6 @@
     <t>Kolmogorov_Complexity</t>
   </si>
   <si>
-    <t>Length_OfURL</t>
-  </si>
-  <si>
     <t>Longest_Word</t>
   </si>
   <si>
@@ -1226,13 +1189,28 @@
   </si>
   <si>
     <t>Short_Url</t>
+  </si>
+  <si>
+    <t>Length_Of_URL</t>
+  </si>
+  <si>
+    <t>FractalDimension</t>
+  </si>
+  <si>
+    <t>Having_Query</t>
+  </si>
+  <si>
+    <t>Count_Http</t>
+  </si>
+  <si>
+    <t>Count_Https</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1277,6 +1255,14 @@
       <name val="Consolas"/>
       <family val="3"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1332,10 +1318,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1365,9 +1352,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1379,11 +1363,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1695,12 +1697,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="J1" t="s">
         <v>194</v>
       </c>
@@ -4698,27 +4700,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66078BF-7097-A04E-85DC-24CEE7935F32}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
-    <col min="7" max="7" width="39" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="39" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>343</v>
       </c>
     </row>
@@ -4726,613 +4728,809 @@
       <c r="A3" t="s">
         <v>342</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G4" s="13"/>
+      <c r="E4" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="G5" s="13"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="G6" s="13"/>
+      <c r="E6" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>156</v>
       </c>
-      <c r="E7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="12"/>
+      <c r="E7" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>160</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="G8" s="13"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>164</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G10" s="13"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="G14" s="13"/>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="A15" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>351</v>
       </c>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G18" s="13"/>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="G19" s="13"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="A20" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="G20" s="13"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G21" s="13"/>
+      <c r="A21" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>359</v>
-      </c>
-      <c r="G22" s="13"/>
+      <c r="A22" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G23" s="13"/>
+        <v>229</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="G24" s="12"/>
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G25" s="13"/>
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>363</v>
+        <v>10</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>364</v>
+        <v>26</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>229</v>
+        <v>318</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" t="s">
-        <v>365</v>
+        <v>31</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>366</v>
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>367</v>
+        <v>338</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" t="s">
-        <v>368</v>
+        <v>341</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" t="s">
-        <v>369</v>
+      <c r="A34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>370</v>
+      <c r="A35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>371</v>
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>372</v>
+        <v>340</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" t="s">
-        <v>373</v>
+        <v>122</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="A40" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>341</v>
-      </c>
-      <c r="E44" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>340</v>
-      </c>
-      <c r="E48" t="s">
-        <v>380</v>
+        <v>37</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>122</v>
-      </c>
-      <c r="E49" t="s">
-        <v>122</v>
+        <v>15</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>381</v>
+      <c r="A50" t="s">
+        <v>339</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E53" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" t="s">
-        <v>385</v>
+      <c r="A54" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>386</v>
+      <c r="A55" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" t="s">
-        <v>387</v>
+      <c r="A56" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>388</v>
+        <v>323</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>211</v>
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="E59" t="s">
-        <v>389</v>
+      <c r="A59" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" t="s">
-        <v>390</v>
+        <v>9</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>339</v>
-      </c>
-      <c r="E61" t="s">
-        <v>339</v>
+      <c r="A61" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>397</v>
+      <c r="A62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>391</v>
+        <v>331</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="A64" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:E66">
+    <sortCondition ref="E44:E66"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="E12" r:id="rId1" xr:uid="{2DBA5242-5AD0-4898-8D60-9C8B808C3867}"/>
+    <hyperlink ref="A12" r:id="rId2" xr:uid="{49C5205B-2E77-4669-A129-4F10AB0D4234}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84D1330A-157F-4E17-B217-9AA8A2BBE511}">
+  <dimension ref="A1:A52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>28</v>
-      </c>
-      <c r="E69" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+    </row>
+    <row r="49" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>39</v>
-      </c>
-      <c r="E73" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+    </row>
+    <row r="52" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>228</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A75">
-    <sortCondition ref="A2:A75"/>
-  </sortState>
+  <hyperlinks>
+    <hyperlink ref="A11" r:id="rId1" xr:uid="{2D09D3D5-010F-4830-9AF1-E0B7C2850821}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/url_features_table.xlsx
+++ b/url_features_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CE3E9C-BDCC-4CAC-9B67-0D90B7976A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263E5EE-3ED5-49B4-B6FA-5CBBE8CFCF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">feature_result!$E$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa1!$A$1:$A$118</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
